--- a/sampleFIles/holidaysBulk.xlsx
+++ b/sampleFIles/holidaysBulk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="10960"/>
+    <workbookView windowWidth="28800" windowHeight="11500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
-  <si>
-    <t>Branch_ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
   <si>
     <t>Name</t>
   </si>
@@ -1145,50 +1142,38 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="1">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="2">
         <v>45950</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="1">
-        <v>8</v>
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="2">
         <v>45950</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="1">
-        <v>9</v>
+    <row r="4" customHeight="1" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" s="2">
         <v>45950</v>
       </c>
     </row>
